--- a/PKGameLabs-Executive-Workstreams.xlsx
+++ b/PKGameLabs-Executive-Workstreams.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workstreams" sheetId="1" r:id="Rf5cf6a795ba34336"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive direction" sheetId="2" r:id="R3c50611f09d448ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Authority and evidence" sheetId="3" r:id="R20dc18dfae064c0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workstreams" sheetId="1" r:id="R7d8adf807cfb4ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive direction" sheetId="2" r:id="R417cc4cd2e9b423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Authority and evidence" sheetId="3" r:id="R41b63d9860ea42fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -128,7 +128,7 @@
         <x:color rgb="FF9D3029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE5E2"/>
         </x:patternFill>
       </x:fill>
@@ -139,7 +139,7 @@
         <x:color rgb="FF805B15"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0D9"/>
         </x:patternFill>
       </x:fill>
@@ -150,7 +150,7 @@
         <x:color rgb="FF6A3983"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4E8FA"/>
         </x:patternFill>
       </x:fill>
@@ -161,7 +161,7 @@
         <x:color rgb="FF5A6574"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDF2"/>
         </x:patternFill>
       </x:fill>
@@ -435,7 +435,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>Reviewed October 5, 2026 (EDT). Status is delivery health, not a personnel rating.</x:v>
+        <x:v>Reviewed October 5, 2026, 03:49 EDT intake. Unchanged rows retain prior evidence. Status describes delivery health.</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -479,13 +479,13 @@
         <x:v>In progress</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Executive decisions adopted; C-Suite becomes the single executive reporting home. Website remains the primary delivery obligation.</x:v>
+        <x:v>Website prototype now reported with working player-reference features and PKQuest art. C-Suite reporting is published.</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Produce a concrete website handoff; reconcile authority and conflicting workstream reports.</x:v>
+        <x:v>Close website brand direction and launch scope with Marketing. Prioritize interactive Windows acceptance.</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>No new approval needed. Website delivery is mine to close.</x:v>
+        <x:v>Help secure a hardware Windows playtest and keep launch scope bounded.</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str"/>
     </x:row>
@@ -515,13 +515,13 @@
         <x:v>At risk</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Integrated Windows candidate built and exact test pair verified. R29 remains governing; deployed game has not advanced with that candidate.</x:v>
+        <x:v>Integrated game deployed with matched PKTest 0.7.3. Windows New Game, radar and control-bridge smoke pass. Full acceptance remains open.</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Finish runtime bindings, deploy matching bytes, obtain fresh Windows gameplay/visual/performance evidence.</x:v>
+        <x:v>Complete interactive gameplay, visual and hardware-performance evidence on the exact deployed pair. Finish remaining runtime bindings.</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Highest leverage: ensure the authorized Windows execution lane has an available operator and machine.</x:v>
+        <x:v>Highest leverage: arrange a hardware Windows playtest with an accountable operator.</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str"/>
     </x:row>
@@ -533,13 +533,13 @@
         <x:v>Dependent</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>Recovered New Player producer semantics are integrated in a new Windows candidate; contract checks pass. This is not gameplay acceptance.</x:v>
+        <x:v>A189 numeric rendering is merged and Windows build/contracts pass. Deployed smoke-tested game still uses the earlier source.</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Close new producer/consumer identity and custody evidence; consume fresh W01–W18 results. Oblivion schema work remains a separate dependency.</x:v>
+        <x:v>Validate A189 in its own deployed candidate. Integrate Oblivion Core semantics and required acceptance fixtures.</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>No new design decision evidenced. Keep acceptance tied to the exact new pair.</x:v>
+        <x:v>No new design decision evidenced. Source completion does not establish deployed acceptance.</x:v>
       </x:c>
       <x:c r="F9" s="12" t="str"/>
     </x:row>
@@ -551,13 +551,13 @@
         <x:v>Dependent</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>Acceptance tooling is prepared. PKStudio now lists PKTest 0.7.1; the inspected integrated game lock uses 0.7.0.</x:v>
+        <x:v>PKTest 0.7.3 runtime repair deployed. Matched Windows smoke passes New Game, radar and control bridge; 9 native regressions pass.</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>Run W01–W18 on the exact locked Windows pair. Using 0.7.1 requires a fresh lock and fresh evidence.</x:v>
+        <x:v>Complete W01–W18 and hardware visual/performance acceptance. Historical 0.7.0 locks remain historical.</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>Existing Windows-lane authorization stands; help with execution access only if still unavailable.</x:v>
+        <x:v>Windows automation access is demonstrated. Help with interactive hardware testing rather than a generic lane procurement.</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str"/>
     </x:row>
@@ -584,16 +584,16 @@
         <x:v>Art Director</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>Reconcile</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>Spawn-100 art closed at 11,047 approved placements; named NPC models ready. Full production-art approval authority is active.</x:v>
+        <x:v>Creature-lane conflict reconciled: directional coverage is active; five separate boss packages remain contract-gated. Art approval queue is growing.</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>Resolve differing Wave-1 lane reports: Director reports production can proceed; PKArt still reports missing contracts.</x:v>
+        <x:v>Review exact creature bindings and Bone/Keeper candidates. Resolve website branding request and remaining boss contracts.</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>No second Executive art gate. Chief Integrator reconciles scope and receipt identity.</x:v>
+        <x:v>No second Executive art gate. Protect Art Director review capacity and prioritize the queue.</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str"/>
     </x:row>
@@ -605,13 +605,13 @@
         <x:v>Dependent</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>Spawn-100 final art package is approved; grass family is closed. Wave-1 preflight identifies missing IDs, profiles and consumer bindings.</x:v>
+        <x:v>Zone-1 batch registers 15 creatures and 120 static directional/corpse frames for review. Oblivion profiles and Lantern door consumer now supplied.</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>Match each production lane to Content/Wiring contracts and current Art Director order; then return discrete approved families.</x:v>
+        <x:v>Consume new contracts, obtain Art Director dispositions and export exact runtime assets. UI effects still need accepted stable IDs.</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>No blanket pixel-production approval needed. Escalate only a concrete authority conflict.</x:v>
+        <x:v>Help enforce handoff closure. Review boards and binding metadata are not approved runtime deliveries.</x:v>
       </x:c>
       <x:c r="F13" s="12" t="str"/>
     </x:row>
@@ -623,13 +623,13 @@
         <x:v>Dependent</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>Art–Content interface v2 defines stable semantics and one Oblivion family: 11 wearables plus 2 separate tools.</x:v>
+        <x:v>Oblivion Core expands the unified family to 12 wearables plus 2 tools. Adaptive behavior contract and 25 acceptance fixtures are specified.</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>Resolve exact boss/item/profile contracts and authored Story Spot/location inputs; coordinate spatial anchors with Map/Wiring.</x:v>
+        <x:v>Build/Wiring must implement and validate Core identity, adaptation, atomic equipment changes and persistence.</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>No unresolved Executive design choice verified; current requests are specialist handoffs.</x:v>
+        <x:v>No new Executive choice evidenced. Preserve one item identity across adaptation and trade.</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str"/>
     </x:row>
@@ -641,13 +641,13 @@
         <x:v>In progress</x:v>
       </x:c>
       <x:c r="C15" s="6" t="str">
-        <x:v>Specialist deliveries now include Phase75 dialogue parity, Phase76 shared Hideouts and Phase77 location recovery. Publication is not adoption.</x:v>
+        <x:v>Published 13 Oblivion presentation profiles plus existing Core profile, and the open/closed Lantern door contract for four consumers.</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>Integrate the current specialist changes and reconcile PKArt bindings; preserve identities and saved state.</x:v>
+        <x:v>PKArt must consume these contracts; Build Master must integrate matching art and runtime bindings.</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>None identified. Keep adoption responsibility with Build Master.</x:v>
+        <x:v>None identified. Previously missing contracts now need acknowledged adoption.</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str"/>
     </x:row>
@@ -695,13 +695,13 @@
         <x:v>Dependent</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>Content and Art Studio 0.6.3 are listed as runnable; PKTest 0.7.1 is listed. Native selected-target identity checks passed on Windows.</x:v>
+        <x:v>Content and Art Studio 0.6.3 remain listed; PKTest is now 0.7.3. Runtime repair explicitly does not embed PKTest in Master Control.</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>Deliver Master Control host, target previews, validators and certified atomic LIVE LOCAL publishing.</x:v>
+        <x:v>Deliver integrated Master Control TEST and certify atomic LIVE LOCAL publishing. Studio currently writes drafts only.</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>No new approval evidenced. Packaging success does not close publisher certification.</x:v>
+        <x:v>Keep runtime packaging, suite integration and publisher certification as separate closure checks.</x:v>
       </x:c>
       <x:c r="F18" s="12" t="str"/>
     </x:row>
@@ -731,13 +731,13 @@
         <x:v>At risk</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>Department reports Strategy, Copy, PR and launch controls ready; Creative remains dependent on captures. Five named lead appointments are not verified.</x:v>
+        <x:v>Website prototype reports working search, reference viewer and preparation tools using PKQuest art. Website-specific branding approval is pending.</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>Hand off website content and approved Windows visuals; verify destinations and named functional ownership.</x:v>
+        <x:v>Obtain Art Director brand direction and a scoped launch roadmap. Account, download, raffle and community services are not live.</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>Reconcile existing appointments before procuring duplicates. Activate any truly vacant Strategy/Copy seats first.</x:v>
+        <x:v>Prioritize real player services and PKQuest branding. Named lead appointments remain unverified.</x:v>
       </x:c>
       <x:c r="F20" s="12" t="str"/>
     </x:row>
@@ -791,7 +791,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cf10ad7d52f4a23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re383c153474840eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -943,10 +943,10 @@
         <x:v>Website</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>Tibia-inspired experience; no external ads. Chief Integrator accountable; Marketing supplies content and launch preparation.</x:v>
+        <x:v>Use Tibia as a functional reference for player services and navigation. Use PKQuest art and Art Director branding. No external ads. Chief Integrator accountable.</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>Executive decision intake</x:v>
+        <x:v>Executive correction recorded in Marketing branding check-in, October 5, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -1022,7 +1022,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc572e7e72b4f451a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b8511b64af14394"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1056,7 +1056,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>Sources reviewed October 5, 2026. Reported updates and unresolved conflicts are explicitly qualified.</x:v>
+        <x:v>October 5, 2026, 03:49 EDT intake. New primary evidence replaces affected rows; other rows retain earlier qualifications.</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1095,13 +1095,13 @@
         <x:v>Reports to Executive; PK Game Labs scope; continuity and succession owner.</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Direct Executive instructions in this conversation, 2026-10-05.</x:v>
+        <x:v>Marketing–Art Director branding check-in, 2026-10-05 (07:31Z); C-Suite main e1d4785.</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Direct instruction</x:v>
+        <x:v>Primary producer report + verified repo</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Website accountability retained; no team interruption or appointment invented.</x:v>
+        <x:v>Website functionality is producer-reported, not independently exercised in this refresh.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
@@ -1129,13 +1129,13 @@
         <x:v>Technical integration, packed runtime, build/release acceptance. New Build Master succession remains governing.</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>https://github.com/houdinicap/PKGameLabs/blob/f8db5ea9531872a26f6b528d51c85d8d432d9076/WORKSTREAM-CHECKPOINT.md</x:v>
+        <x:v>PKGameLabs-BuildMaster-Status.json v69, pkTestRuntimeRepair; GitHub run 37271845473; checkpoint d6b017243be387ccab1bd1c57275bc97fd1a26c5.</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Primary Git checkpoint</x:v>
+        <x:v>Primary Build Master record</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Newer appended integration evidence supersedes stale v68 coordination-summary blockers. Historical A159 archive absence is not the blocker for the new integrated pair.</x:v>
+        <x:v>Game f3752788… / PKTest 952928a6… matched. Hosted Windows Mesa llvmpipe smoke is not hardware performance or full acceptance.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
@@ -1146,13 +1146,13 @@
         <x:v>Gameplay/state contracts; Build Master owns adopted source and binaries.</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>https://github.com/houdinicap/PKGameLabs/blob/f8db5ea9531872a26f6b528d51c85d8d432d9076/WORKSTREAM-CHECKPOINT.md; latest AI conversation return retrieved 2026-10-05.</x:v>
+        <x:v>PKQuest-AI-Framework-R29-A189-Implementation-Receipt-2026-10-05.md; Build Master v69 runtime repair.</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Primary + reported update</x:v>
+        <x:v>Primary specialist + integrator records</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>Integrated candidate identity differs from original A159/A159R. No inherited Windows acceptance.</x:v>
+        <x:v>51 renderer/edge checks, 38 topology checks, 22 recipe checks reported passing. A189 is not the deployed smoke-tested binary.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
@@ -1163,13 +1163,13 @@
         <x:v>Test tooling and evidence; no self-certification of an unexecuted game.</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>https://github.com/houdinicap/PKGameLabs/blob/f8db5ea9531872a26f6b528d51c85d8d432d9076/WORKSTREAM-CHECKPOINT.md; https://github.com/houdinicap/PKStudio/blob/main/README.md</x:v>
+        <x:v>Build Master v69 pkTestRuntimeRepair; https://github.com/houdinicap/PKStudio/blob/main/README.md</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>Primary Git files</x:v>
+        <x:v>Primary integrator + repository</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>PKTest 0.7.1 availability does not alter the inspected 0.7.0 game lock.</x:v>
+        <x:v>0.7.3-runtime-repair is a new matched pair. Smoke passes; fullAcceptance=false. Historical 0.7.0 locks unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
@@ -1197,13 +1197,13 @@
         <x:v>Executive-delegated full artistic direction and production-art approval.</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>PKQ-AD-R29-READY-016; PKQ-AD-R29-COVERAGE-015; latest Art Director return retrieved 2026-10-05.</x:v>
+        <x:v>PKArt ACTIVE-CREATURE-LANE-REVIEW-v1; ZONE1-CREATURE-BINDING-BATCH-v1-REVIEW; BONE-KEEPER-ART-DIRECTOR-REVIEW-INTAKE-v1; Marketing branding check-in (all 2026-10-05).</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>Primary + reported update</x:v>
+        <x:v>Primary producer handoffs</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>Later Director report names a different production order; reconcile by exact lane rather than assuming PKArt is cleared.</x:v>
+        <x:v>Directional lane and five COVERAGE-015 boss packages are distinct. Pending reviews do not imply approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
@@ -1214,13 +1214,13 @@
         <x:v>Production assets under Art Director; no gameplay identity/footprint authority.</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>PKQuest-PKArt-R29-WAVE1-UNBLOCK-REQUEST.json; Oblivion delta review; PKQ-AD-R29-READY-016.</x:v>
+        <x:v>PKArt Zone1 creature batch review v1; ContentWiring Oblivion profiles v1 and Lantern door consumer v1; UI &amp; Effects Combat Effect Preflight v1 (2026-10-05).</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>Primary files + later report</x:v>
+        <x:v>Primary producer contracts</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>Content interface v2 has logical Oblivion targets; PKArt still requests exact per-definition profile reconciliation. This is an intake conflict, not proven global absence.</x:v>
+        <x:v>15 creatures / 120 frames are binding metadata awaiting Art Director review. Armor-stop and resisted-magic labels are not accepted runtime IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
@@ -1231,13 +1231,13 @@
         <x:v>Semantic IDs, gameplay identities, logical presentation contracts; Map owns coordinates.</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>PKQuest-Art-Content-Interface-Manifest-v2.txt; Warehouse Checkpoint07; PKArt Wave1 request.</x:v>
+        <x:v>PKQuest-Oblivion-Core-Integration-Handoff-v1.txt, Content Pack150, 2026-10-05.</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>Primary files</x:v>
+        <x:v>Primary semantic contract</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>11 wearable Oblivion definitions; Shovel/Pickaxe excluded from wearable set membership.</x:v>
+        <x:v>12 wearable definitions including Core, plus 2 nonwearable tools. 25 fixtures are required, not reported executed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
@@ -1248,13 +1248,13 @@
         <x:v>Runtime contract wiring and specialist implementations; Build Master integrates.</x:v>
       </x:c>
       <x:c r="C15" s="6" t="str">
-        <x:v>Library inventory: Phase75 (05:26Z), Phase76 (05:36Z), Phase77 (05:49Z), 2026-10-05; Warehouse Checkpoint07.</x:v>
+        <x:v>PKQuest-ContentWiring-R29-OBLIVION-PRESENTATION-PROFILES-v1-2026-10-05.json; PKQuest-ContentWiring-R29-LANTERN-DOOR-OPEN-CONSUMER-v1-2026-10-05.json.</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>Package existence + primary context</x:v>
+        <x:v>Primary contract files</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>Latest ZIP bodies not audited in this intake; no tests or runtime adoption inferred from filenames.</x:v>
+        <x:v>13 newly resolved profiles plus Core. Four door consumers share one open state family. No art approval or integration acceptance claimed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
@@ -1299,13 +1299,13 @@
         <x:v>Studio tools; Build Master target services and integration; LIVE LOCAL certification boundary remains.</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>https://github.com/houdinicap/PKStudio/blob/main/README.md; https://github.com/houdinicap/PKGameLabs/blob/f8db5ea9531872a26f6b528d51c85d8d432d9076/WORKSTREAM-CHECKPOINT.md</x:v>
+        <x:v>https://github.com/houdinicap/PKStudio/blob/main/README.md (PKTest0.7.3); Build Master v69 pkTestRuntimeRepair.</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>Primary Git files</x:v>
+        <x:v>Primary repository + integrator</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>0.6.4 was reported as an unsaved attempt; do not present it as deployed.</x:v>
+        <x:v>masterControlEmbedding=false. Studio draft writing does not enable authoritative promotion.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
@@ -1333,13 +1333,13 @@
         <x:v>VP owns Marketing; functional leaders within department; Chronicle independent.</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>Marketing Chief Integrator check-in; procurement manifest; Snapshot2; latest Marketing Department conversation return.</x:v>
+        <x:v>PKQuest-Marketing-ArtDirector-Branding-Checkin-2026-10-05.txt (07:31Z).</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>Primary files + reported update</x:v>
+        <x:v>Primary Marketing report</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>Active department reported; individual named seat appointments still need reconciliation. No duplicate staffing demand.</x:v>
+        <x:v>Working features are reported, not independently tested. Brand request receipt/reply unconfirmed. Public launch services remain incomplete.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
@@ -1379,7 +1379,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1a6fafc56ee43ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8611854dd1141ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>